--- a/tools/_out/groupB_20261021/stage/04_DESIGN_TABLES/DesignTable_6901.xlsx
+++ b/tools/_out/groupB_20261021/stage/04_DESIGN_TABLES/DesignTable_6901.xlsx
@@ -2469,12 +2469,36 @@
           <t>6901-04-04-NWO-FG</t>
         </is>
       </c>
+      <c r="B32" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.6879999999999999</v>
+      </c>
       <c r="F32" t="n">
         <v>0.5629999999999999</v>
       </c>
+      <c r="G32" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.22</v>
+      </c>
       <c r="J32" t="n">
         <v>0.4375</v>
       </c>
+      <c r="K32" t="n">
+        <v>0.54</v>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>6901-04-04-NWO-FG</t>
@@ -2487,12 +2511,12 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6901-04-04 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: N5@DRIVE, M1@DRIVE, W3@HEX, CHEX@HEX, C1HEX@HEX, D1@BORE, D@BORE] [BRENNAN-CAD 2026-10-21: C4HEX@HEX, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6901-04-04 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6901-04-04 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6901-04-04-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6901-04-04 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6901-04-04-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | Brennan CAD record 6901-04-04-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: N5@DRIVE=M7, M1@DRIVE=M, W3@HEX=M6, CHEX@HEX=C1, C1HEX@HEX=Y, D1@BORE=BD, D@BORE=AD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -2517,12 +2541,36 @@
           <t>6901-04-06-NWO-FG</t>
         </is>
       </c>
+      <c r="B33" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.875</v>
+      </c>
       <c r="F33" t="n">
         <v>0.5629999999999999</v>
       </c>
+      <c r="G33" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.34</v>
+      </c>
       <c r="J33" t="n">
         <v>0.4375</v>
       </c>
+      <c r="K33" t="n">
+        <v>0.675</v>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>6901-04-06-NWO-FG</t>
@@ -2535,12 +2583,12 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6901-04-06 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: N5@DRIVE, M1@DRIVE, W3@HEX, CHEX@HEX, C1HEX@HEX, D1@BORE, D@BORE] [BRENNAN-CAD 2026-10-21: C4HEX@HEX, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6901-04-06 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6901-04-06 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6901-04-06-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6901-04-06 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6901-04-06-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | Brennan CAD record 6901-04-06-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: N5@DRIVE=M7, M1@DRIVE=M, W3@HEX=M6, CHEX@HEX=C1, C1HEX@HEX=Y, D1@BORE=BD, D@BORE=AD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -2565,12 +2613,36 @@
           <t>6901-06-08-NWO-FG</t>
         </is>
       </c>
+      <c r="B34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
       <c r="F34" t="n">
         <v>0.6879999999999999</v>
       </c>
+      <c r="G34" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.45</v>
+      </c>
       <c r="J34" t="n">
         <v>0.5625</v>
       </c>
+      <c r="K34" t="n">
+        <v>0.84</v>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>6901-06-08-NWO-FG</t>
@@ -2583,12 +2655,12 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6901-06-08 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: N5@DRIVE, M1@DRIVE, W3@HEX, CHEX@HEX, C1HEX@HEX, D1@BORE, D@BORE] [BRENNAN-CAD 2026-10-21: C4HEX@HEX, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6901-06-08 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6901-06-08 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6901-06-08-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6901-06-08 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6901-06-08-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | Brennan CAD record 6901-06-08-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: N5@DRIVE=M7, M1@DRIVE=M, W3@HEX=M6, CHEX@HEX=C1, C1HEX@HEX=Y, D1@BORE=BD, D@BORE=AD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -2613,12 +2685,36 @@
           <t>6901-10-12-NWO-FG</t>
         </is>
       </c>
+      <c r="B35" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.25</v>
+      </c>
       <c r="F35" t="n">
         <v>1</v>
       </c>
+      <c r="G35" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.62</v>
+      </c>
       <c r="J35" t="n">
         <v>0.875</v>
       </c>
+      <c r="K35" t="n">
+        <v>1.05</v>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>6901-10-12-NWO-FG</t>
@@ -2631,12 +2727,12 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6901-10-12 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: N5@DRIVE, M1@DRIVE, W3@HEX, CHEX@HEX, C1HEX@HEX, D1@BORE, D@BORE] [BRENNAN-CAD 2026-10-21: C4HEX@HEX, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6901-10-12 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6901-10-12 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6901-10-12-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6901-10-12 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6901-10-12-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | Brennan CAD record 6901-10-12-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: N5@DRIVE=M7, M1@DRIVE=M, W3@HEX=M6, CHEX@HEX=C1, C1HEX@HEX=Y, D1@BORE=BD, D@BORE=AD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -2661,12 +2757,36 @@
           <t>6901-12-06-NWO-FG</t>
         </is>
       </c>
+      <c r="B36" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.875</v>
+      </c>
       <c r="F36" t="n">
         <v>1.25</v>
       </c>
+      <c r="G36" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.34</v>
+      </c>
       <c r="J36" t="n">
         <v>1.0625</v>
       </c>
+      <c r="K36" t="n">
+        <v>0.675</v>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>6901-12-06-NWO-FG</t>
@@ -2679,12 +2799,12 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6901-12-06 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: N5@DRIVE, M1@DRIVE, W3@HEX, CHEX@HEX, C1HEX@HEX, D1@BORE, D@BORE] [BRENNAN-CAD 2026-10-21: C4HEX@HEX, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6901-12-06 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6901-12-06 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6901-12-06-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6901-12-06 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6901-12-06-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | Brennan CAD record 6901-12-06-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: N5@DRIVE=M7, M1@DRIVE=M, W3@HEX=M6, CHEX@HEX=C1, C1HEX@HEX=Y, D1@BORE=BD, D@BORE=AD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -2709,12 +2829,36 @@
           <t>6901-12-08-NWO-FG</t>
         </is>
       </c>
+      <c r="B37" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
       <c r="F37" t="n">
         <v>1.25</v>
       </c>
+      <c r="G37" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.46</v>
+      </c>
       <c r="J37" t="n">
         <v>1.0625</v>
       </c>
+      <c r="K37" t="n">
+        <v>0.84</v>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>6901-12-08-NWO-FG</t>
@@ -2727,12 +2871,12 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6901-12-08 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: N5@DRIVE, M1@DRIVE, W3@HEX, CHEX@HEX, C1HEX@HEX, D1@BORE, D@BORE] [BRENNAN-CAD 2026-10-21: C4HEX@HEX, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6901-12-08 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6901-12-08 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6901-12-08-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6901-12-08 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6901-12-08-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | Brennan CAD record 6901-12-08-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: N5@DRIVE=M7, M1@DRIVE=M, W3@HEX=M6, CHEX@HEX=C1, C1HEX@HEX=Y, D1@BORE=BD, D@BORE=AD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -2757,12 +2901,36 @@
           <t>6901-12-12-NWO-FG</t>
         </is>
       </c>
+      <c r="B38" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.25</v>
+      </c>
       <c r="F38" t="n">
         <v>1.25</v>
       </c>
+      <c r="G38" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.62</v>
+      </c>
       <c r="J38" t="n">
         <v>1.0625</v>
       </c>
+      <c r="K38" t="n">
+        <v>1.05</v>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>6901-12-12-NWO-FG</t>
@@ -2775,12 +2943,12 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6901-12-12 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: N5@DRIVE, M1@DRIVE, W3@HEX, CHEX@HEX, C1HEX@HEX, D1@BORE, D@BORE] [BRENNAN-CAD 2026-10-21: C4HEX@HEX, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6901-12-12 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6901-12-12 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6901-12-12-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6901-12-12 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6901-12-12-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | Brennan CAD record 6901-12-12-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: N5@DRIVE=M7, M1@DRIVE=M, W3@HEX=M6, CHEX@HEX=C1, C1HEX@HEX=Y, D1@BORE=BD, D@BORE=AD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -2805,12 +2973,36 @@
           <t>6901-12-16-NWO-FG</t>
         </is>
       </c>
+      <c r="B39" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.5</v>
+      </c>
       <c r="F39" t="n">
         <v>1.25</v>
       </c>
+      <c r="G39" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.79</v>
+      </c>
       <c r="J39" t="n">
         <v>1.0625</v>
       </c>
+      <c r="K39" t="n">
+        <v>1.315</v>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>6901-12-16-NWO-FG</t>
@@ -2823,12 +3015,12 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6901-12-16 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: N5@DRIVE, M1@DRIVE, W3@HEX, CHEX@HEX, C1HEX@HEX, D1@BORE, D@BORE] [BRENNAN-CAD 2026-10-21: C4HEX@HEX, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6901-12-16 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6901-12-16 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6901-12-16-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6901-12-16 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6901-12-16-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | Brennan CAD record 6901-12-16-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: N5@DRIVE=M7, M1@DRIVE=M, W3@HEX=M6, CHEX@HEX=C1, C1HEX@HEX=Y, D1@BORE=BD, D@BORE=AD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -2853,12 +3045,36 @@
           <t>6901-16-12-NWO-FG</t>
         </is>
       </c>
+      <c r="B40" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.25</v>
+      </c>
       <c r="F40" t="n">
         <v>1.5</v>
       </c>
+      <c r="G40" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.62</v>
+      </c>
       <c r="J40" t="n">
         <v>1.3125</v>
       </c>
+      <c r="K40" t="n">
+        <v>1.05</v>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>6901-16-12-NWO-FG</t>
@@ -2871,12 +3087,12 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6901-16-12 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: N5@DRIVE, M1@DRIVE, W3@HEX, CHEX@HEX, C1HEX@HEX, D1@BORE, D@BORE] [BRENNAN-CAD 2026-10-21: C4HEX@HEX, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6901-16-12 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6901-16-12 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6901-16-12-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6901-16-12 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6901-16-12-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | Brennan CAD record 6901-16-12-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: N5@DRIVE=M7, M1@DRIVE=M, W3@HEX=M6, CHEX@HEX=C1, C1HEX@HEX=Y, D1@BORE=BD, D@BORE=AD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -2901,12 +3117,36 @@
           <t>6901-16-16-NWO-FG</t>
         </is>
       </c>
+      <c r="B41" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.5</v>
+      </c>
       <c r="F41" t="n">
         <v>1.5</v>
       </c>
+      <c r="G41" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.83</v>
+      </c>
       <c r="J41" t="n">
         <v>1.3125</v>
       </c>
+      <c r="K41" t="n">
+        <v>1.315</v>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>6901-16-16-NWO-FG</t>
@@ -2919,12 +3159,12 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6901-16-16 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: N5@DRIVE, M1@DRIVE, W3@HEX, CHEX@HEX, C1HEX@HEX, D1@BORE, D@BORE] [BRENNAN-CAD 2026-10-21: C4HEX@HEX, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6901-16-16 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6901-16-16 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6901-16-16-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6901-16-16 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6901-16-16-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | Brennan CAD record 6901-16-16-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: N5@DRIVE=M7, M1@DRIVE=M, W3@HEX=M6, CHEX@HEX=C1, C1HEX@HEX=Y, D1@BORE=BD, D@BORE=AD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -2949,12 +3189,36 @@
           <t>6901-20-16-NWO-FG</t>
         </is>
       </c>
+      <c r="B42" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.5</v>
+      </c>
       <c r="F42" t="n">
         <v>1.875</v>
       </c>
+      <c r="G42" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.831</v>
+      </c>
       <c r="J42" t="n">
         <v>1.625</v>
       </c>
+      <c r="K42" t="n">
+        <v>1.315</v>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>6901-20-16-NWO-FG</t>
@@ -2967,12 +3231,12 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6901-20-16 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: N5@DRIVE, M1@DRIVE, W3@HEX, CHEX@HEX, C1HEX@HEX, D1@BORE, D@BORE] [BRENNAN-CAD 2026-10-21: C4HEX@HEX, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6901-20-16 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6901-20-16 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6901-20-16-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6901-20-16 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6901-20-16-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | Brennan CAD record 6901-20-16-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: N5@DRIVE=M7, M1@DRIVE=M, W3@HEX=M6, CHEX@HEX=C1, C1HEX@HEX=Y, D1@BORE=BD, D@BORE=AD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -2997,12 +3261,36 @@
           <t>6901-20-20-NWO-FG</t>
         </is>
       </c>
+      <c r="B43" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.875</v>
+      </c>
       <c r="F43" t="n">
         <v>1.875</v>
       </c>
+      <c r="G43" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.087</v>
+      </c>
       <c r="J43" t="n">
         <v>1.625</v>
       </c>
+      <c r="K43" t="n">
+        <v>1.66</v>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>6901-20-20-NWO-FG</t>
@@ -3015,12 +3303,12 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6901-20-20 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: N5@DRIVE, M1@DRIVE, W3@HEX, CHEX@HEX, C1HEX@HEX, D1@BORE, D@BORE] [BRENNAN-CAD 2026-10-21: C4HEX@HEX, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6901-20-20 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6901-20-20 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6901-20-20-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6901-20-20 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6901-20-20-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | Brennan CAD record 6901-20-20-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: N5@DRIVE=M7, M1@DRIVE=M, W3@HEX=M6, CHEX@HEX=C1, C1HEX@HEX=Y, D1@BORE=BD, D@BORE=AD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -3045,12 +3333,36 @@
           <t>6901-24-24-NWO-FG</t>
         </is>
       </c>
+      <c r="B44" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2.125</v>
+      </c>
       <c r="F44" t="n">
         <v>2.125</v>
       </c>
+      <c r="G44" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1.317</v>
+      </c>
       <c r="J44" t="n">
         <v>1.875</v>
       </c>
+      <c r="K44" t="n">
+        <v>1.9</v>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>6901-24-24-NWO-FG</t>
@@ -3063,12 +3375,12 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6901-24-24 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: N5@DRIVE, M1@DRIVE, W3@HEX, CHEX@HEX, C1HEX@HEX, D1@BORE, D@BORE] [BRENNAN-CAD 2026-10-21: C4HEX@HEX, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6901-24-24 NWO (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6901-24-24 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6901-24-24-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6901-24-24 NWO dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6901-24-24-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | Brennan CAD record 6901-24-24-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: N5@DRIVE=M7, M1@DRIVE=M, W3@HEX=M6, CHEX@HEX=C1, C1HEX@HEX=Y, D1@BORE=BD, D@BORE=AD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -3093,12 +3405,36 @@
           <t>6901-32-32-NWO-FG</t>
         </is>
       </c>
+      <c r="B45" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="C45" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2.625</v>
+      </c>
       <c r="F45" t="n">
         <v>2.75</v>
       </c>
+      <c r="G45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.781</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1.802</v>
+      </c>
       <c r="J45" t="n">
         <v>2.5</v>
       </c>
+      <c r="K45" t="n">
+        <v>2.375</v>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>6901-32-32-NWO-FG</t>
@@ -3111,12 +3447,12 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: N5@DRIVE, M1@DRIVE, W3@HEX, CHEX@HEX, C1HEX@HEX, D1@BORE, D@BORE] [BRENNAN-CAD 2026-10-21: C4HEX@HEX, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | Brennan CAD record 6901-32-32-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | Brennan CAD record 6901-32-32-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | Brennan CAD record 6901-32-32-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: N5@DRIVE=M7, M1@DRIVE=M, W3@HEX=M6, CHEX@HEX=C1, C1HEX@HEX=Y, D1@BORE=BD, D@BORE=AD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -3141,15 +3477,30 @@
           <t>6901-08-06-NWO-FG</t>
         </is>
       </c>
+      <c r="B46" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1.2</v>
+      </c>
       <c r="E46" t="n">
         <v>0.875</v>
       </c>
       <c r="F46" t="n">
         <v>0.875</v>
       </c>
+      <c r="G46" t="n">
+        <v>0.75</v>
+      </c>
       <c r="H46" t="n">
         <v>0.391</v>
       </c>
+      <c r="I46" t="n">
+        <v>0.34</v>
+      </c>
       <c r="J46" t="n">
         <v>0.75</v>
       </c>
@@ -3168,17 +3519,17 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): nut / locknut hexes / bores from the Brennan TFA catalog p.45; legs and body flats NOT proposed (catalog letters do not pair with the Air-Way rows)</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: N5@DRIVE, M1@DRIVE, W3@HEX, C1HEX@HEX, D@BORE] [BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): nut / locknut hexes / bores from the Brennan TFA catalog p.45; legs and body flats NOT proposed (catalog letters do not pair with the Air-Way rows)</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; hexes / bores from the Brennan TFA catalog p.45 alone; legs / flats open; marked DimSource BRENNAN</t>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; hexes / bores from the Brennan TFA catalog p.45 alone; legs / flats open; marked DimSource BRENNAN | Brennan CAD record 6901-08-06-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: N5@DRIVE=M7, M1@DRIVE=M, W3@HEX=M6, C1HEX@HEX=Y, D@BORE=AD; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -3203,12 +3554,24 @@
           <t>6901-08-12-NWO-FG</t>
         </is>
       </c>
+      <c r="B47" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1.58</v>
+      </c>
       <c r="E47" t="n">
         <v>1.25</v>
       </c>
       <c r="F47" t="n">
         <v>0.875</v>
       </c>
+      <c r="G47" t="n">
+        <v>1.062</v>
+      </c>
       <c r="H47" t="n">
         <v>0.391</v>
       </c>
@@ -3233,17 +3596,17 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): nut / locknut hexes / bores from the Brennan TFA catalog p.45; legs and body flats NOT proposed (catalog letters do not pair with the Air-Way rows)</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: N5@DRIVE, M1@DRIVE, W3@HEX, C1HEX@HEX] [BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): nut / locknut hexes / bores from the Brennan TFA catalog p.45; legs and body flats NOT proposed (catalog letters do not pair with the Air-Way rows)</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; hexes / bores from the Brennan TFA catalog p.45 alone; legs / flats open; marked DimSource BRENNAN</t>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; hexes / bores from the Brennan TFA catalog p.45 alone; legs / flats open; marked DimSource BRENNAN | Brennan CAD record 6901-08-12-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: N5@DRIVE=M7, M1@DRIVE=M, W3@HEX=M6, C1HEX@HEX=Y; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -3268,12 +3631,24 @@
           <t>6901-10-06-NWO-FG</t>
         </is>
       </c>
+      <c r="B48" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1.25</v>
+      </c>
       <c r="E48" t="n">
         <v>0.875</v>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
+      <c r="G48" t="n">
+        <v>0.875</v>
+      </c>
       <c r="H48" t="n">
         <v>0.484</v>
       </c>
@@ -3298,17 +3673,17 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): nut / locknut hexes / bores from the Brennan TFA catalog p.45; legs and body flats NOT proposed (catalog letters do not pair with the Air-Way rows)</t>
+          <t>[BRENNAN-CAD 2026-10-21 group B: N5@DRIVE, M1@DRIVE, W3@HEX, C1HEX@HEX] [BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): nut / locknut hexes / bores from the Brennan TFA catalog p.45; legs and body flats NOT proposed (catalog letters do not pair with the Air-Way rows)</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; hexes / bores from the Brennan TFA catalog p.45 alone; legs / flats open; marked DimSource BRENNAN</t>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; hexes / bores from the Brennan TFA catalog p.45 alone; legs / flats open; marked DimSource BRENNAN | Brennan CAD record 6901-10-06-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: N5@DRIVE=M7, M1@DRIVE=M, W3@HEX=M6, C1HEX@HEX=Y; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">

--- a/tools/_out/groupB_20261021/stage/04_DESIGN_TABLES/DesignTable_6901.xlsx
+++ b/tools/_out/groupB_20261021/stage/04_DESIGN_TABLES/DesignTable_6901.xlsx
@@ -3606,7 +3606,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; hexes / bores from the Brennan TFA catalog p.45 alone; legs / flats open; marked DimSource BRENNAN | Brennan CAD record 6901-08-12-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: N5@DRIVE=M7, M1@DRIVE=M, W3@HEX=M6, C1HEX@HEX=Y; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; hexes / bores from the Brennan TFA catalog p.45 alone; legs / flats open; marked DimSource BRENNAN | BRENNAN_6901-08-12-NWO-FG (received 2026-10-21, tools/measure/npsm.py): the swivel end = NPSM_MEAS[12] (the 1404-12 end) on every value, nut face 1.580, stem tip 1.270 (= the record M6 / M), body hex 1.062 - the record is right. Still generator-BLOCKED: the swivel neck is only 0.015 long (body face 0.76 behind the nut face, nut rear face 0.745; the generator wants &gt;= 0.02) and the forged corner (puck radius 0.613) reaches 0.004 into the ORB locknut slab (starts 0.609; Brennan ends the corner at the ORB body face 0.59) - needs a generator change (group B README) | Brennan CAD record 6901-08-12-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: N5@DRIVE=M7, M1@DRIVE=M, W3@HEX=M6, C1HEX@HEX=Y; user 2026-10-21 "yes you can use them following my rule")</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
